--- a/data/trans_camb/P16A12-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,96</t>
+          <t>2,63; 8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,7</t>
+          <t>4,25; 11,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,51</t>
+          <t>2,75; 9,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 8,27</t>
+          <t>2,16; 7,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,22</t>
+          <t>2,75; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,99</t>
+          <t>4,76; 10,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,34</t>
+          <t>3,26; 7,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,22</t>
+          <t>3,88; 8,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,11</t>
+          <t>5,08; 9,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,61; 84,69</t>
+          <t>18,2; 86,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,38; 104,31</t>
+          <t>32,31; 107,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,04; 91,73</t>
+          <t>22,09; 92,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 69,11</t>
+          <t>14,87; 67,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,06; 78,34</t>
+          <t>19,22; 79,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,51; 88,39</t>
+          <t>32,03; 87,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 64,55</t>
+          <t>24,87; 67,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,35; 82,46</t>
+          <t>29,53; 79,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,52; 80,96</t>
+          <t>38,87; 82,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,44</t>
+          <t>-0,87; 1,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,89</t>
+          <t>1,29; 3,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,96</t>
+          <t>1,36; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,3</t>
+          <t>0,14; 2,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,47</t>
+          <t>1,05; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,91</t>
+          <t>0,65; 2,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,56</t>
+          <t>-0,09; 1,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,34</t>
+          <t>1,5; 3,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,68</t>
+          <t>1,39; 3,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 53,87</t>
+          <t>-22,72; 57,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,93; 152,72</t>
+          <t>32,94; 148,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,2; 189,97</t>
+          <t>41,58; 187,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 169,81</t>
+          <t>3,15; 166,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,22; 255,82</t>
+          <t>43,3; 252,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,02; 208,98</t>
+          <t>27,52; 218,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 71,63</t>
+          <t>-3,51; 70,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 158,25</t>
+          <t>51,34; 153,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,05; 160,88</t>
+          <t>49,19; 163,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,18</t>
+          <t>-0,78; 3,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,35</t>
+          <t>0,07; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,21</t>
+          <t>2,06; 6,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,81</t>
+          <t>-1,63; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,88</t>
+          <t>-1,33; 1,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,14</t>
+          <t>-0,76; 2,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,98</t>
+          <t>-0,73; 1,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,53</t>
+          <t>-0,15; 2,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,71</t>
+          <t>1,14; 3,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 249,25</t>
+          <t>-36,82; 324,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 384,72</t>
+          <t>-12,69; 405,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,18; 536,74</t>
+          <t>66,99; 568,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 279,22</t>
+          <t>-72,38; 254,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 250,27</t>
+          <t>-57,78; 275,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 314,44</t>
+          <t>-29,98; 307,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 164,74</t>
+          <t>-36,61; 161,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 205,93</t>
+          <t>-9,99; 215,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,62; 341,13</t>
+          <t>42,62; 316,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,89</t>
+          <t>0,53; 2,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,94</t>
+          <t>1,58; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,85</t>
+          <t>0,37; 3,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,78</t>
+          <t>1,21; 3,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,05</t>
+          <t>0,52; 3,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,93</t>
+          <t>-0,61; 1,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,9</t>
+          <t>1,16; 2,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,18</t>
+          <t>1,43; 3,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,61</t>
+          <t>0,6; 2,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,94; 58,25</t>
+          <t>8,49; 59,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,83; 77,04</t>
+          <t>25,69; 80,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,2; 74,35</t>
+          <t>7,56; 75,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,93; 69,09</t>
+          <t>17,97; 65,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 55,5</t>
+          <t>8,09; 57,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 34,51</t>
+          <t>-8,96; 36,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 53,59</t>
+          <t>17,58; 51,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,96; 58,71</t>
+          <t>22,47; 57,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,47; 47,49</t>
+          <t>10,63; 47,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A12-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A12-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,85</t>
+          <t>2,36; 8,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,21</t>
+          <t>4,32; 11,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,42</t>
+          <t>1,96; 8,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,81</t>
+          <t>2,29; 7,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,99</t>
+          <t>2,7; 9,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,08</t>
+          <t>4,29; 10,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,63</t>
+          <t>3,32; 7,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,97</t>
+          <t>4,17; 8,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,36</t>
+          <t>4,33; 8,62</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,2; 86,36</t>
+          <t>18,36; 85,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,31; 107,24</t>
+          <t>33,69; 113,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 92,27</t>
+          <t>15,7; 83,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,87; 67,78</t>
+          <t>15,86; 68,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,22; 79,2</t>
+          <t>18,95; 81,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,03; 87,86</t>
+          <t>29,24; 87,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,87; 67,42</t>
+          <t>24,05; 66,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,53; 79,69</t>
+          <t>31,1; 76,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,87; 82,63</t>
+          <t>32,24; 75,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>3,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,47</t>
+          <t>-0,77; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,98</t>
+          <t>1,16; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,93</t>
+          <t>2,92; 5,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,4</t>
+          <t>0,1; 2,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,39</t>
+          <t>1,14; 3,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,89</t>
+          <t>1,41; 3,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,52</t>
+          <t>-0,03; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,23</t>
+          <t>1,49; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,62</t>
+          <t>2,56; 4,22</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108,67%</t>
+          <t>132,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>105,63%</t>
+          <t>134,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106,45%</t>
+          <t>132,01%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 57,78</t>
+          <t>-21,44; 61,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,94; 148,27</t>
+          <t>27,92; 146,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,58; 187,57</t>
+          <t>73,94; 208,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 166,87</t>
+          <t>2,5; 162,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,3; 252,29</t>
+          <t>45,3; 267,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,52; 218,12</t>
+          <t>55,57; 260,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 70,6</t>
+          <t>-2,39; 71,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,34; 153,16</t>
+          <t>48,63; 145,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,19; 163,26</t>
+          <t>83,56; 199,24</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,31</t>
+          <t>-0,75; 3,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,33</t>
+          <t>0,08; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,01</t>
+          <t>2,06; 6,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,67</t>
+          <t>-1,63; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,91</t>
+          <t>-1,36; 1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,14</t>
+          <t>-0,72; 2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,92</t>
+          <t>-0,76; 1,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,44</t>
+          <t>-0,13; 2,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,61</t>
+          <t>1,29; 3,78</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214,26%</t>
+          <t>223,81%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>139,58%</t>
+          <t>147,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 324,55</t>
+          <t>-35,79; 304,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 405,06</t>
+          <t>-8,72; 385,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,99; 568,27</t>
+          <t>61,14; 572,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 254,99</t>
+          <t>-75,48; 242,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 275,69</t>
+          <t>-59,63; 215,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 307,81</t>
+          <t>-31,22; 311,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 161,45</t>
+          <t>-36,49; 167,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 215,39</t>
+          <t>-12,25; 228,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42,62; 316,26</t>
+          <t>51,04; 361,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>2,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,93</t>
+          <t>0,46; 2,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,05</t>
+          <t>1,53; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,84</t>
+          <t>1,87; 4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,64</t>
+          <t>1,18; 3,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,11</t>
+          <t>0,51; 3,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,96</t>
+          <t>0,4; 2,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,79</t>
+          <t>1,22; 2,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,11</t>
+          <t>1,51; 3,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,56</t>
+          <t>1,47; 3,1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 59,51</t>
+          <t>7,36; 57,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,69; 80,28</t>
+          <t>24,81; 81,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,56; 75,72</t>
+          <t>28,84; 85,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,97; 65,68</t>
+          <t>17,19; 66,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 57,67</t>
+          <t>7,57; 55,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 36,28</t>
+          <t>5,65; 42,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,58; 51,15</t>
+          <t>19,45; 55,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,47; 57,17</t>
+          <t>24,83; 60,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 47,22</t>
+          <t>23,54; 58,29</t>
         </is>
       </c>
     </row>
